--- a/data/trans_bre/IP16A08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 12,78</t>
+          <t>-25,66; 12,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 10,42</t>
+          <t>-29,49; 8,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 28,4</t>
+          <t>-14,39; 25,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 7,1</t>
+          <t>-12,67; 7,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 29,63</t>
+          <t>-13,52; 28,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 26,24</t>
+          <t>-6,92; 27,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 18,6</t>
+          <t>-19,08; 18,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 9,73</t>
+          <t>-16,62; 9,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,21; 710,51</t>
+          <t>-59,15; 582,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,85; 774,12</t>
+          <t>-51,33; 738,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,48; 255,6</t>
+          <t>-66,86; 282,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,98; 132,51</t>
+          <t>-86,78; 162,5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 19,83</t>
+          <t>-29,22; 20,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 10,4</t>
+          <t>-16,11; 9,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-42,09; 13,3</t>
+          <t>-41,79; 14,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,75; -0,55</t>
+          <t>-26,56; -3,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 16,7</t>
+          <t>-31,88; 14,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 12,4</t>
+          <t>-21,06; 12,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 22,24</t>
+          <t>-5,55; 22,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,26</t>
+          <t>0,0; 37,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 231,32</t>
+          <t>-100,0; 189,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 49,4</t>
+          <t>-23,7; 50,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,19</t>
+          <t>0,0; 36,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-54,84; 0,0</t>
+          <t>-67,54; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 0,0</t>
+          <t>-58,72; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,58; 17,57</t>
+          <t>-45,4; 18,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,59; 23,61</t>
+          <t>-23,05; 22,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 29,0</t>
+          <t>-42,75; 26,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 24,77</t>
+          <t>-12,0; 29,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,09; 92,55</t>
+          <t>-79,81; 88,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 344,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 2350266,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 10,74</t>
+          <t>-15,88; 10,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 18,9</t>
+          <t>-12,33; 19,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 34,13</t>
+          <t>-6,07; 34,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 29,15</t>
+          <t>-3,84; 29,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-76,84; 560,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 1151,49</t>
+          <t>-54,25; 817,96</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 12,04</t>
+          <t>-13,08; 11,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 6,09</t>
+          <t>-33,7; 5,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 1,25</t>
+          <t>-31,2; 2,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 5,79</t>
+          <t>-46,58; 6,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,42; 218,92</t>
+          <t>-83,35; 214,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,18; 62,37</t>
+          <t>-89,24; 99,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,8</t>
+          <t>-100,0; 50,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 7,03</t>
+          <t>-7,48; 6,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 5,91</t>
+          <t>-6,68; 6,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 6,46</t>
+          <t>-8,45; 7,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 3,64</t>
+          <t>-8,19; 3,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 55,85</t>
+          <t>-38,72; 53,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 62,87</t>
+          <t>-42,51; 62,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 55,84</t>
+          <t>-43,91; 70,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 50,59</t>
+          <t>-62,8; 52,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 12,49</t>
+          <t>-30,2; 12,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 8,45</t>
+          <t>-26,03; 9,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 25,93</t>
+          <t>-15,77; 25,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 7,73</t>
+          <t>-13,84; 7,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 28,48</t>
+          <t>-11,45; 28,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 27,15</t>
+          <t>-8,29; 26,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 18,65</t>
+          <t>-18,53; 19,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 9,28</t>
+          <t>-14,86; 9,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 582,53</t>
+          <t>-63,22; 693,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 738,07</t>
+          <t>-58,44; 704,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,86; 282,74</t>
+          <t>-67,1; 361,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,78; 162,5</t>
+          <t>-88,39; 153,58</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 20,1</t>
+          <t>-28,91; 19,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 9,75</t>
+          <t>-16,58; 8,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 14,1</t>
+          <t>-41,66; 13,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,56; -3,32</t>
+          <t>-26,58; -3,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 14,42</t>
+          <t>-31,43; 15,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 12,74</t>
+          <t>-22,61; 11,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 22,3</t>
+          <t>-5,25; 23,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,4</t>
+          <t>0,0; 34,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 189,22</t>
+          <t>-100,0; 196,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 50,37</t>
+          <t>-24,34; 46,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,03</t>
+          <t>0,0; 36,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-67,54; 0,0</t>
+          <t>-58,04; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-58,72; 0,0</t>
+          <t>-61,34; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 18,85</t>
+          <t>-41,83; 21,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 22,34</t>
+          <t>-23,29; 22,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 26,62</t>
+          <t>-44,11; 29,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 29,41</t>
+          <t>-11,11; 25,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,81; 88,58</t>
+          <t>-74,94; 95,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,92; 656,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2350266,83</t>
+          <t>-100,0; 5556457,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 10,02</t>
+          <t>-16,1; 10,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 19,17</t>
+          <t>-12,18; 19,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 34,18</t>
+          <t>-6,9; 31,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 29,07</t>
+          <t>-3,19; 28,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,24; 518,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 817,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 11,55</t>
+          <t>-12,19; 12,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 5,92</t>
+          <t>-32,57; 6,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 2,66</t>
+          <t>-29,54; 2,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,58; 6,6</t>
+          <t>-46,93; 3,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,35; 214,2</t>
+          <t>-79,3; 224,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,24; 99,91</t>
+          <t>-89,65; 77,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,33</t>
+          <t>-100,0; 90,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 6,89</t>
+          <t>-7,32; 7,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 6,09</t>
+          <t>-6,75; 5,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 7,19</t>
+          <t>-8,06; 5,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,95</t>
+          <t>-7,72; 3,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 53,68</t>
+          <t>-38,46; 55,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 62,47</t>
+          <t>-42,07; 60,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 70,67</t>
+          <t>-44,31; 55,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 52,54</t>
+          <t>-58,5; 51,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,77</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-29,81%</t>
+          <t>-12,87%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 12,23</t>
+          <t>-25,54; 12,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 9,3</t>
+          <t>-26,13; 10,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 25,28</t>
+          <t>-14,66; 28,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 7,43</t>
+          <t>-14,8; 9,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-18,92%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 28,8</t>
+          <t>-12,4; 29,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 26,29</t>
+          <t>-7,06; 26,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 19,67</t>
+          <t>-19,37; 18,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 9,28</t>
+          <t>-8,46; 15,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,22; 693,38</t>
+          <t>-59,21; 710,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 704,38</t>
+          <t>-48,85; 774,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,1; 361,01</t>
+          <t>-70,48; 255,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,39; 153,58</t>
+          <t>-59,65; 288,16</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-10,69</t>
+          <t>-11,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 19,81</t>
+          <t>-29,56; 19,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 8,8</t>
+          <t>-15,82; 10,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 13,76</t>
+          <t>-42,09; 13,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,58; -3,34</t>
+          <t>-28,32; -3,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>8,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 15,71</t>
+          <t>-31,24; 16,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 11,4</t>
+          <t>-20,12; 12,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 23,77</t>
+          <t>-5,58; 22,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,55</t>
+          <t>0,0; 33,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 196,3</t>
+          <t>-100,0; 231,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-20,54</t>
+          <t>-12,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 46,34</t>
+          <t>-26,02; 49,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,47</t>
+          <t>0,0; 36,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-58,04; 0,0</t>
+          <t>-54,84; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-61,34; 0,0</t>
+          <t>-40,28; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,83; 21,4</t>
+          <t>-42,58; 17,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 22,29</t>
+          <t>-23,59; 23,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 29,67</t>
+          <t>-38,72; 29,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 25,14</t>
+          <t>-11,23; 25,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,94; 95,53</t>
+          <t>-78,09; 92,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,92; 656,84</t>
+          <t>-100,0; 344,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 5556457,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,89</t>
+          <t>12,99</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>146,94%</t>
+          <t>137,14%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 10,97</t>
+          <t>-15,6; 10,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 19,78</t>
+          <t>-12,28; 18,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 31,38</t>
+          <t>-7,46; 34,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 28,28</t>
+          <t>-2,75; 30,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-73,24; 518,84</t>
+          <t>-76,84; 560,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-35,26; 1090,71</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-20,24</t>
+          <t>-21,87</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-73,13%</t>
+          <t>-76,08%</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 12,58</t>
+          <t>-12,7; 12,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,57; 6,01</t>
+          <t>-31,7; 6,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,54; 2,92</t>
+          <t>-30,56; 1,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 3,58</t>
+          <t>-49,78; 2,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,3; 224,87</t>
+          <t>-82,42; 218,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,65; 77,91</t>
+          <t>-89,18; 62,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,85</t>
+          <t>-100,0; 30,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-17,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 7,08</t>
+          <t>-7,67; 7,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 5,7</t>
+          <t>-6,53; 5,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 5,69</t>
+          <t>-8,12; 6,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 3,87</t>
+          <t>-6,03; 6,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 55,48</t>
+          <t>-37,86; 55,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 60,27</t>
+          <t>-42,57; 62,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 55,02</t>
+          <t>-46,22; 55,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 51,23</t>
+          <t>-46,01; 89,15</t>
         </is>
       </c>
     </row>
